--- a/Kachi_Gun/Table/Weapon.xlsx
+++ b/Kachi_Gun/Table/Weapon.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapon_Grade_Growth" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,16 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet_Spec" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -29,19 +28,32 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="007A3E00"/>
+      <color rgb="FF7A3E00"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -53,20 +65,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002D3E50"/>
-        <bgColor rgb="002D3E50"/>
+        <fgColor rgb="FF2D3E50"/>
+        <bgColor rgb="FF2D3E50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008B5A2B"/>
-        <bgColor rgb="008B5A2B"/>
+        <fgColor rgb="FF8B5A2B"/>
+        <bgColor rgb="FF8B5A2B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8DC"/>
-        <bgColor rgb="00FFF8DC"/>
+        <fgColor rgb="FFFFF8DC"/>
+        <bgColor rgb="FFFFF8DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,17 +92,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D4D4D4"/>
+        <color rgb="FFD4D4D4"/>
       </left>
       <right style="thin">
-        <color rgb="00D4D4D4"/>
+        <color rgb="FFD4D4D4"/>
       </right>
       <top style="thin">
-        <color rgb="00D4D4D4"/>
+        <color rgb="FFD4D4D4"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D4D4D4"/>
+        <color rgb="FFD4D4D4"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -127,7 +140,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -491,7 +504,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -504,7 +517,7 @@
     <col width="19" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1" ht="24.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Grade_Idx</t>
@@ -551,7 +564,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="19" customHeight="1">
+    <row r="2" ht="18.95" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>0</v>
       </c>
@@ -588,7 +601,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="19" customHeight="1">
+    <row r="3" ht="18.95" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -625,7 +638,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="19" customHeight="1">
+    <row r="4" ht="18.95" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
@@ -662,7 +675,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="19" customHeight="1">
+    <row r="5" ht="18.95" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -699,7 +712,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="19" customHeight="1">
+    <row r="6" ht="18.95" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
@@ -727,7 +740,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -736,7 +749,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="18.95" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -764,7 +777,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -773,7 +786,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="19" customHeight="1">
+    <row r="8" ht="18.95" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
@@ -801,7 +814,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -810,7 +823,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1">
+    <row r="9" ht="18.95" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -838,7 +851,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -847,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="19" customHeight="1">
+    <row r="10" ht="18.95" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>8</v>
       </c>
@@ -875,7 +888,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -884,7 +897,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="19" customHeight="1">
+    <row r="11" ht="18.95" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -912,7 +925,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -921,7 +934,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19" customHeight="1">
+    <row r="12" ht="18.95" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
@@ -949,7 +962,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -958,7 +971,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19" customHeight="1">
+    <row r="13" ht="18.95" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>11</v>
       </c>
@@ -986,7 +999,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -995,7 +1008,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1">
+    <row r="14" ht="18.95" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>12</v>
       </c>
@@ -1023,7 +1036,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>laser, missile</t>
+          <t>single, shotgun, fast, pierce, laser, missile</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1043,22 +1056,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:S69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="4" max="5"/>
+    <col width="19" customWidth="1" min="6" max="7"/>
+    <col width="11" customWidth="1" min="8" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="12" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
@@ -1067,7 +1076,7 @@
     <col width="17" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1" ht="24.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Code</t>
@@ -1164,7 +1173,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="19" customHeight="1">
+    <row r="2" ht="18.95" customHeight="1">
       <c r="A2" s="3" t="n">
         <v>0</v>
       </c>
@@ -1188,7 +1197,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>리볼버</t>
+          <t>기본탄_D</t>
         </is>
       </c>
       <c r="G2" s="5" t="n">
@@ -1237,7 +1246,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="19" customHeight="1">
+    <row r="3" ht="18.95" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1259,9 +1268,9 @@
           <t>산탄</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>소드오프 샷건</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>산탄_D</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
@@ -1310,7 +1319,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="19" customHeight="1">
+    <row r="4" ht="18.95" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
@@ -1334,7 +1343,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>우지</t>
+          <t>속사탄_D</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
@@ -1383,7 +1392,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="19" customHeight="1">
+    <row r="5" ht="18.95" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>10</v>
       </c>
@@ -1405,9 +1414,9 @@
           <t>단발</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>상위 리볼버</t>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_C</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
@@ -1456,7 +1465,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="19" customHeight="1">
+    <row r="6" ht="18.95" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>11</v>
       </c>
@@ -1478,9 +1487,9 @@
           <t>산탄</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>펌프액션 샷건</t>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>산탄_C</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
@@ -1529,7 +1538,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="18.95" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>13</v>
       </c>
@@ -1553,7 +1562,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>돌격소총</t>
+          <t>관통탄_C</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
@@ -1602,7 +1611,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="19" customHeight="1">
+    <row r="8" ht="18.95" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>20</v>
       </c>
@@ -1626,7 +1635,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>매그넘</t>
+          <t>기본탄_B</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
@@ -1675,7 +1684,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1">
+    <row r="9" ht="18.95" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>21</v>
       </c>
@@ -1697,9 +1706,9 @@
           <t>산탄</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>전투 샷건</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>산탄_B</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
@@ -1748,7 +1757,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="19" customHeight="1">
+    <row r="10" ht="18.95" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>22</v>
       </c>
@@ -1772,7 +1781,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>중기관총</t>
+          <t>속사탄_B</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
@@ -1821,7 +1830,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="19" customHeight="1">
+    <row r="11" ht="18.95" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>23</v>
       </c>
@@ -1843,9 +1852,9 @@
           <t>관통</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>관통 라이플</t>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_B</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
@@ -1894,7 +1903,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19" customHeight="1">
+    <row r="12" ht="18.95" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>30</v>
       </c>
@@ -1916,9 +1925,9 @@
           <t>단발</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>황금 매그넘</t>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_A</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
@@ -1967,7 +1976,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19" customHeight="1">
+    <row r="13" ht="18.95" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>31</v>
       </c>
@@ -1989,9 +1998,9 @@
           <t>산탄</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>드래곤 샷건</t>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>산탄_A</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
@@ -2040,7 +2049,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1">
+    <row r="14" ht="18.95" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>32</v>
       </c>
@@ -2064,7 +2073,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>미니건</t>
+          <t>속사탄_A</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
@@ -2113,7 +2122,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1">
+    <row r="15" ht="18.95" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>33</v>
       </c>
@@ -2135,9 +2144,9 @@
           <t>관통</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>레일 라이플</t>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_A</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
@@ -2186,9 +2195,9 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1">
+    <row r="16" ht="18.95" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>4</v>
@@ -2200,17 +2209,17 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>laser</t>
+          <t>single</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>레이저</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>레이저 건</t>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_S</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
@@ -2225,7 +2234,7 @@
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>1</v>
@@ -2234,34 +2243,34 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>2571.4</v>
+        <v>1500</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>20571.2</v>
+        <v>1500</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>2.57k</t>
+          <t>1.5k</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>S등급 레이저</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1">
+          <t>S등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18.95" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>4</v>
@@ -2273,221 +2282,221 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>missile</t>
+          <t>shotgun</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>미사일</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>미사일 런처</t>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>산탄_S</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>3000</v>
+        <v>2.25</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>428</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>3k</t>
+          <t>428</t>
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="6" t="n">
-        <v>1.6</v>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>2307.7</v>
+        <v>2334.5</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>11538.5</v>
+        <v>2334.5</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>2.3k</t>
+          <t>2.33k</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>S등급 미사일</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1">
+          <t>S등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18.95" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_S</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>1.8k</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>S등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18.95" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_S</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>675</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>laser</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>레이저</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>플라즈마 레이저</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>1.8k</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>48000</v>
-      </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>6k</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>SS등급 레이저</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>미사일</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>다연장 미사일</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>6k</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>1.7</v>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O19" s="6" t="n">
         <v>9</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>10000</v>
+        <v>675</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>50000</v>
+        <v>3375</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>675</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>SS등급 미사일</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1">
+          <t>S등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18.95" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>SSS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -2500,24 +2509,24 @@
           <t>레이저</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>오메가 레이저</t>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_S</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>3600</v>
+        <v>2.25</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>900</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>3.6k</t>
+          <t>900</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>1</v>
@@ -2532,430 +2541,430 @@
         <v>0</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>14400</v>
+        <v>2571.4</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>115200</v>
+        <v>20571.2</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>14.4k</t>
+          <t>2.57k</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>SSS등급 레이저</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1">
+          <t>S등급 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18.95" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>미사일</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_S</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>3k</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>2307.7</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>11538.5</v>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>2.3k</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>S등급 미사일</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18.95" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_SS</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>1.8k</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>3k</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>SS등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18.95" customHeight="1">
+      <c r="A23" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>산탄_SS</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>855</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K23" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>SSS</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>미사일</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>핵 미사일</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n">
+      <c r="L23" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>4663.6</v>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>4663.6</v>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>4.66k</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>SS등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18.95" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_SS</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>12k</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="6" t="n">
+      <c r="H24" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>3600</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>3600</v>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>3.6k</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>SS등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18.95" customHeight="1">
+      <c r="A25" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_SS</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="O21" s="6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>32727.3</v>
-      </c>
-      <c r="Q21" s="8" t="n">
-        <v>163636.5</v>
-      </c>
-      <c r="R21" s="4" t="inlineStr">
-        <is>
-          <t>32.7k</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>SSS등급 미사일</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="H25" s="8" t="n">
+        <v>1350</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>1.35k</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>6750</v>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>1.35k</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>SS등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18.95" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>laser</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>레이저</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>하이퍼 레이저</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>7920</v>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>7.92k</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>33000</v>
-      </c>
-      <c r="Q22" s="8" t="n">
-        <v>264000</v>
-      </c>
-      <c r="R22" s="4" t="inlineStr">
-        <is>
-          <t>33k</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>R등급 레이저</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>미사일</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>전술 핵 미사일</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>26400</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>26.4k</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="P23" s="8" t="n">
-        <v>74717</v>
-      </c>
-      <c r="Q23" s="8" t="n">
-        <v>373585</v>
-      </c>
-      <c r="R23" s="4" t="inlineStr">
-        <is>
-          <t>74.7k</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>R등급 미사일</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>SR</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>laser</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>레이저</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>퀘이사 레이저</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>17424</v>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>17.4k</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>75756.5</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>606052</v>
-      </c>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>75.7k</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>SR등급 레이저</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>SR</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>미사일</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>반물질 미사일</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>58080</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>58k</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O25" s="6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>170823.5</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>854117.5</v>
-      </c>
-      <c r="R25" s="4" t="inlineStr">
-        <is>
-          <t>170k</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>SR등급 미사일</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>SSR</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>laser</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>레이저</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>네뷸라 레이저</t>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_SS</t>
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>43560</v>
+        <v>1800</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>43.5k</t>
+          <t>1.8k</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>1</v>
@@ -2970,430 +2979,430 @@
         <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>9.949999999999999</v>
+        <v>9</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>198000</v>
+        <v>6000</v>
       </c>
       <c r="Q26" s="8" t="n">
-        <v>1584000</v>
+        <v>48000</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>198k</t>
+          <t>6k</t>
         </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>SSR등급 레이저</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="19" customHeight="1">
+          <t>SS등급 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18.95" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="B27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>미사일</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_SS</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>6k</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O27" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>SSR</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>미사일</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>중력자 미사일</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>145200</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>145k</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O27" s="6" t="n">
-        <v>9.949999999999999</v>
-      </c>
       <c r="P27" s="8" t="n">
-        <v>592653.1</v>
+        <v>10000</v>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>2963265.5</v>
+        <v>50000</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>592k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>SSR등급 미사일</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1">
+          <t>SS등급 미사일</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18.95" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>SSS</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_SSS</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>3.6k</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>6k</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>SSS등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18.95" customHeight="1">
+      <c r="A29" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SSS</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>산탄_SSS</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1710</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>1.71k</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>9327.299999999999</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>9327.299999999999</v>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>9.32k</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>SSS등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18.95" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>SSS</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_SSS</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>1.8k</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P30" s="8" t="n">
+        <v>7200</v>
+      </c>
+      <c r="Q30" s="8" t="n">
+        <v>7200</v>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>7.2k</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>SSS등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18.95" customHeight="1">
+      <c r="A31" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>SSS</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_SSS</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>13500</v>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>2.7k</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>SSS등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18.95" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>SSS</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
           <t>laser</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>레이저</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>노바 레이저</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>108900</v>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>108k</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>518571.4</v>
-      </c>
-      <c r="Q28" s="8" t="n">
-        <v>4148571.2</v>
-      </c>
-      <c r="R28" s="4" t="inlineStr">
-        <is>
-          <t>518k</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>U등급 레이저</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>미사일</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>초신성 미사일</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>363000</v>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>363k</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="P29" s="8" t="n">
-        <v>1544680.9</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>7723404.5</v>
-      </c>
-      <c r="R29" s="4" t="inlineStr">
-        <is>
-          <t>1.54m</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>U등급 미사일</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>laser</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>레이저</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>보이드 레이저</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>304920</v>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>304k</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="P30" s="8" t="n">
-        <v>1524600</v>
-      </c>
-      <c r="Q30" s="8" t="n">
-        <v>12196800</v>
-      </c>
-      <c r="R30" s="4" t="inlineStr">
-        <is>
-          <t>1.52m</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>SU등급 레이저</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>SU</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>미사일</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>차원파괴 미사일</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>1016400</v>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>1.01m</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>5646666.7</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>28233333.5</v>
-      </c>
-      <c r="R31" s="4" t="inlineStr">
-        <is>
-          <t>5.64m</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>SU등급 미사일</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>SSU</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>laser</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>레이저</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>제네시스 레이저</t>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_SSS</t>
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>914760</v>
+        <v>3600</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>914k</t>
+          <t>3.6k</t>
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>1</v>
@@ -3407,94 +3416,2722 @@
       <c r="N32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="O32" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>14400</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>115200</v>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>14.4k</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>SSS등급 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18.95" customHeight="1">
+      <c r="A33" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>SSS</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>미사일</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_SSS</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>12k</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>32727.3</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>163636.5</v>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>32.7k</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>SSS등급 미사일</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_R</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>7920</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>7.92k</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>13.2k</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>R등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>산탄_R</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>3762</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>3.76k</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>20520</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>20520</v>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>20.5k</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>R등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_R</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>3960</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>3.96k</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>15840</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>15840</v>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>15.8k</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>R등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_R</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>5940</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>5.94k</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>5940</v>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>29700</v>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>5.94k</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>R등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>laser</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>레이저</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_R</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>7920</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>7.92k</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="6" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>33000</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>264000</v>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>33k</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>R등급 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>미사일</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_R</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>26400</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>26.4k</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O39" s="6" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>74717</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>373585</v>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>74.7k</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>R등급 미사일</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_SR</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>17424</v>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>17.4k</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <v>29040</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>29040</v>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>29k</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>SR등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>산탄_SR</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>8276</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>8.27k</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>45141.8</v>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>45141.8</v>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>45.1k</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>SR등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_SR</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>8712</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>8.71k</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>34848</v>
+      </c>
+      <c r="Q42" s="8" t="n">
+        <v>34848</v>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>34.8k</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>SR등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_SR</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>13068</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>13k</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>13068</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>65340</v>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>13k</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>SR등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>laser</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>레이저</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_SR</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>17424</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>17.4k</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P44" s="8" t="n">
+        <v>75756.5</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>606052</v>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>75.7k</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>SR등급 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>미사일</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_SR</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>58080</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>58k</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P45" s="8" t="n">
+        <v>170823.5</v>
+      </c>
+      <c r="Q45" s="8" t="n">
+        <v>854117.5</v>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>170k</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>SR등급 미사일</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_SSR</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>43560</v>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>43.5k</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P46" s="8" t="n">
+        <v>72600</v>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>72600</v>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>72.6k</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>SSR등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>산탄_SSR</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>20691</v>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>20.6k</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P47" s="8" t="n">
+        <v>112860</v>
+      </c>
+      <c r="Q47" s="8" t="n">
+        <v>112860</v>
+      </c>
+      <c r="R47" s="4" t="inlineStr">
+        <is>
+          <t>112k</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>SSR등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_SSR</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>21780</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>21.7k</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>87120</v>
+      </c>
+      <c r="Q48" s="8" t="n">
+        <v>87120</v>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>87.1k</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>SSR등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_SSR</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>32670</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>32.6k</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>32670</v>
+      </c>
+      <c r="Q49" s="8" t="n">
+        <v>163350</v>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>32.6k</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>SSR등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>laser</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>레이저</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_SSR</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>43560</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>43.5k</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>198000</v>
+      </c>
+      <c r="Q50" s="8" t="n">
+        <v>1584000</v>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>198k</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>SSR등급 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>SSR</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>미사일</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_SSR</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>145200</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>145k</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>592653.1</v>
+      </c>
+      <c r="Q51" s="8" t="n">
+        <v>2963265.5</v>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>592k</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>SSR등급 미사일</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_U</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>108900</v>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>108k</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P52" s="8" t="n">
+        <v>181500</v>
+      </c>
+      <c r="Q52" s="8" t="n">
+        <v>181500</v>
+      </c>
+      <c r="R52" s="4" t="inlineStr">
+        <is>
+          <t>181k</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>U등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>산탄_U</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>51728</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>51.7k</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P53" s="8" t="n">
+        <v>282152.7</v>
+      </c>
+      <c r="Q53" s="8" t="n">
+        <v>282152.7</v>
+      </c>
+      <c r="R53" s="4" t="inlineStr">
+        <is>
+          <t>282k</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>U등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_U</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>54450</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>54.4k</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P54" s="8" t="n">
+        <v>217800</v>
+      </c>
+      <c r="Q54" s="8" t="n">
+        <v>217800</v>
+      </c>
+      <c r="R54" s="4" t="inlineStr">
+        <is>
+          <t>217k</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>U등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_U</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>81675</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>81.6k</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P55" s="8" t="n">
+        <v>81675</v>
+      </c>
+      <c r="Q55" s="8" t="n">
+        <v>408375</v>
+      </c>
+      <c r="R55" s="4" t="inlineStr">
+        <is>
+          <t>81.6k</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>U등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>laser</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>레이저</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_U</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>108900</v>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>108k</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="P56" s="8" t="n">
+        <v>518571.4</v>
+      </c>
+      <c r="Q56" s="8" t="n">
+        <v>4148571.2</v>
+      </c>
+      <c r="R56" s="4" t="inlineStr">
+        <is>
+          <t>518k</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>U등급 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>미사일</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_U</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>363000</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>363k</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="P57" s="8" t="n">
+        <v>1544680.9</v>
+      </c>
+      <c r="Q57" s="8" t="n">
+        <v>7723404.5</v>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>1.54m</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>U등급 미사일</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_SU</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>304920</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>304k</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P58" s="8" t="n">
+        <v>508200</v>
+      </c>
+      <c r="Q58" s="8" t="n">
+        <v>508200</v>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>508k</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>SU등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>산탄_SU</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>144837</v>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>144k</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P59" s="8" t="n">
+        <v>790020</v>
+      </c>
+      <c r="Q59" s="8" t="n">
+        <v>790020</v>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>790k</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>SU등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_SU</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>152460</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>152k</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P60" s="8" t="n">
+        <v>609840</v>
+      </c>
+      <c r="Q60" s="8" t="n">
+        <v>609840</v>
+      </c>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>609k</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>SU등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_SU</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>228690</v>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>228k</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P61" s="8" t="n">
+        <v>228690</v>
+      </c>
+      <c r="Q61" s="8" t="n">
+        <v>1143450</v>
+      </c>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>228k</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>SU등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>laser</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>레이저</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_SU</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>304920</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>304k</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="P62" s="8" t="n">
+        <v>1524600</v>
+      </c>
+      <c r="Q62" s="8" t="n">
+        <v>12196800</v>
+      </c>
+      <c r="R62" s="4" t="inlineStr">
+        <is>
+          <t>1.52m</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>SU등급 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>미사일</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_SU</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>1016400</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>1.01m</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="P63" s="8" t="n">
+        <v>5646666.7</v>
+      </c>
+      <c r="Q63" s="8" t="n">
+        <v>28233333.5</v>
+      </c>
+      <c r="R63" s="4" t="inlineStr">
+        <is>
+          <t>5.64m</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>SU등급 미사일</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>SSU</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>단발</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>기본탄_SSU</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>914760</v>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>914k</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P64" s="8" t="n">
+        <v>1524600</v>
+      </c>
+      <c r="Q64" s="8" t="n">
+        <v>1524600</v>
+      </c>
+      <c r="R64" s="4" t="inlineStr">
+        <is>
+          <t>1.52m</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>SSU등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>SSU</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>shotgun</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>산탄</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>산탄_SSU</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>434511</v>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>434k</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P65" s="8" t="n">
+        <v>2370060</v>
+      </c>
+      <c r="Q65" s="8" t="n">
+        <v>2370060</v>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>2.37m</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>SSU등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>SSU</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>속사</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>속사탄_SSU</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>457380</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>457k</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P66" s="8" t="n">
+        <v>1829520</v>
+      </c>
+      <c r="Q66" s="8" t="n">
+        <v>1829520</v>
+      </c>
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>1.82m</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>SSU등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>SSU</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>관통</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>관통탄_SSU</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>686070</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>686k</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P67" s="8" t="n">
+        <v>686070</v>
+      </c>
+      <c r="Q67" s="8" t="n">
+        <v>3430350</v>
+      </c>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>686k</t>
+        </is>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>SSU등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>SSU</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>laser</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>레이저</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>레이저탄_SSU</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>914760</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>914k</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="P32" s="8" t="n">
+      <c r="P68" s="8" t="n">
         <v>4814526.3</v>
       </c>
-      <c r="Q32" s="8" t="n">
+      <c r="Q68" s="8" t="n">
         <v>38516210.4</v>
       </c>
-      <c r="R32" s="4" t="inlineStr">
+      <c r="R68" s="4" t="inlineStr">
         <is>
           <t>4.81m</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S68" s="7" t="inlineStr">
         <is>
           <t>SSU등급 레이저</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="3" t="n">
+    <row r="69">
+      <c r="A69" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B69" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>SSU</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>missile</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>미사일</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>아포칼립스 미사일</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="n">
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>미사일탄_SSU</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H69" s="8" t="n">
         <v>3049200</v>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
         <is>
           <t>3.04m</t>
         </is>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J69" s="6" t="n">
         <v>0.86</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K69" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L69" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" s="6" t="n">
+      <c r="M69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" s="6" t="n">
         <v>2.72</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="O69" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="P33" s="8" t="n">
+      <c r="P69" s="8" t="n">
         <v>17727907</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="Q69" s="8" t="n">
         <v>88639535</v>
       </c>
-      <c r="R33" s="4" t="inlineStr">
+      <c r="R69" s="4" t="inlineStr">
         <is>
           <t>17.7m</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S69" s="7" t="inlineStr">
         <is>
           <t>SSU등급 미사일</t>
         </is>
@@ -3502,6 +6139,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3512,10 +6150,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -3523,12 +6160,10 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="10" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1" ht="24.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
@@ -3590,7 +6225,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="19" customHeight="1">
+    <row r="2" ht="18.95" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>single</t>
@@ -3629,16 +6264,16 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>Bullet/bullet_basic</t>
+          <t>Bullet/bullet_plain</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>UI/icon_pistol</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="19" customHeight="1">
+          <t>Bullet/icon_single</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.95" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>shotgun</t>
@@ -3682,11 +6317,11 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>Bullet/shotgun_icon</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="19" customHeight="1">
+          <t>Bullet/icon_shotgun</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18.95" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>fast</t>
@@ -3730,11 +6365,11 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Bullet/bullet_basic</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="19" customHeight="1">
+          <t>Bullet/icon_fast</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.95" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>pierce</t>
@@ -3778,11 +6413,11 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Bullet/drill</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1">
+          <t>Bullet/icon_pierce</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.95" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>laser</t>
@@ -3826,11 +6461,11 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Bullet/laser_icon</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1">
+          <t>Bullet/icon_laser</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18.95" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>missile</t>
@@ -3874,7 +6509,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Bullet/missile</t>
+          <t>Bullet/icon_missile</t>
         </is>
       </c>
     </row>

--- a/Kachi_Gun/Table/Weapon.xlsx
+++ b/Kachi_Gun/Table/Weapon.xlsx
@@ -1056,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S69"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1074,6 +1074,7 @@
     <col width="24" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.95" customHeight="1">
@@ -1172,6 +1173,11 @@
           <t>Impl_Note</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Merge_Weight (%)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18.95" customHeight="1">
       <c r="A2" s="3" t="n">
@@ -1245,6 +1251,9 @@
           <t>D등급 기본 지급</t>
         </is>
       </c>
+      <c r="T2" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" ht="18.95" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -1317,6 +1326,9 @@
         <is>
           <t>D등급 산탄</t>
         </is>
+      </c>
+      <c r="T3" s="7" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="4" ht="18.95" customHeight="1">
@@ -1391,6 +1403,9 @@
           <t>D등급 속사</t>
         </is>
       </c>
+      <c r="T4" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" ht="18.95" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -1464,6 +1479,9 @@
           <t>C등급 단발</t>
         </is>
       </c>
+      <c r="T5" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" ht="18.95" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -1537,6 +1555,9 @@
           <t>C등급 산탄</t>
         </is>
       </c>
+      <c r="T6" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="7" ht="18.95" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -1610,6 +1631,9 @@
           <t>C등급 관통</t>
         </is>
       </c>
+      <c r="T7" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" ht="18.95" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -1683,6 +1707,9 @@
           <t>B등급 단발</t>
         </is>
       </c>
+      <c r="T8" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" ht="18.95" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -1756,6 +1783,9 @@
           <t>B등급 산탄</t>
         </is>
       </c>
+      <c r="T9" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" ht="18.95" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -1829,6 +1859,9 @@
           <t>B등급 속사</t>
         </is>
       </c>
+      <c r="T10" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" ht="18.95" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -1902,6 +1935,9 @@
           <t>B등급 관통</t>
         </is>
       </c>
+      <c r="T11" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" ht="18.95" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1975,6 +2011,9 @@
           <t>A등급 단발</t>
         </is>
       </c>
+      <c r="T12" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" ht="18.95" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -2048,6 +2087,9 @@
           <t>A등급 산탄</t>
         </is>
       </c>
+      <c r="T13" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" ht="18.95" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -2121,6 +2163,9 @@
           <t>A등급 속사</t>
         </is>
       </c>
+      <c r="T14" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" ht="18.95" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -2194,6 +2239,9 @@
           <t>A등급 관통</t>
         </is>
       </c>
+      <c r="T15" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="16" ht="18.95" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -2267,6 +2315,9 @@
           <t>S등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T16" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="17" ht="18.95" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -2340,6 +2391,9 @@
           <t>S등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T17" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="18" ht="18.95" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -2413,6 +2467,9 @@
           <t>S등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T18" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="19" ht="18.95" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -2486,6 +2543,9 @@
           <t>S등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T19" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" ht="18.95" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -2559,6 +2619,9 @@
           <t>S등급 레이저</t>
         </is>
       </c>
+      <c r="T20" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="21" ht="18.95" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -2632,6 +2695,9 @@
           <t>S등급 미사일</t>
         </is>
       </c>
+      <c r="T21" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" ht="18.95" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -2705,6 +2771,9 @@
           <t>SS등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T22" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="23" ht="18.95" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -2778,6 +2847,9 @@
           <t>SS등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T23" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="24" ht="18.95" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -2851,6 +2923,9 @@
           <t>SS등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T24" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="25" ht="18.95" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -2924,6 +2999,9 @@
           <t>SS등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T25" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="26" ht="18.95" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -2997,6 +3075,9 @@
           <t>SS등급 레이저</t>
         </is>
       </c>
+      <c r="T26" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="27" ht="18.95" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -3070,6 +3151,9 @@
           <t>SS등급 미사일</t>
         </is>
       </c>
+      <c r="T27" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="28" ht="18.95" customHeight="1">
       <c r="A28" s="3" t="n">
@@ -3143,6 +3227,9 @@
           <t>SSS등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T28" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="29" ht="18.95" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -3216,6 +3303,9 @@
           <t>SSS등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T29" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="30" ht="18.95" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -3289,6 +3379,9 @@
           <t>SSS등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T30" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="31" ht="18.95" customHeight="1">
       <c r="A31" s="3" t="n">
@@ -3362,6 +3455,9 @@
           <t>SSS등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T31" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="32" ht="18.95" customHeight="1">
       <c r="A32" s="3" t="n">
@@ -3435,6 +3531,9 @@
           <t>SSS등급 레이저</t>
         </is>
       </c>
+      <c r="T32" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="33" ht="18.95" customHeight="1">
       <c r="A33" s="3" t="n">
@@ -3508,6 +3607,9 @@
           <t>SSS등급 미사일</t>
         </is>
       </c>
+      <c r="T33" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -3581,6 +3683,9 @@
           <t>R등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T34" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -3654,6 +3759,9 @@
           <t>R등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T35" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -3727,6 +3835,9 @@
           <t>R등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T36" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -3800,6 +3911,9 @@
           <t>R등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T37" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -3873,6 +3987,9 @@
           <t>R등급 레이저</t>
         </is>
       </c>
+      <c r="T38" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -3946,6 +4063,9 @@
           <t>R등급 미사일</t>
         </is>
       </c>
+      <c r="T39" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -4019,6 +4139,9 @@
           <t>SR등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T40" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -4092,6 +4215,9 @@
           <t>SR등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T41" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -4165,6 +4291,9 @@
           <t>SR등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T42" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -4238,6 +4367,9 @@
           <t>SR등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T43" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -4311,6 +4443,9 @@
           <t>SR등급 레이저</t>
         </is>
       </c>
+      <c r="T44" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -4384,6 +4519,9 @@
           <t>SR등급 미사일</t>
         </is>
       </c>
+      <c r="T45" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -4457,6 +4595,9 @@
           <t>SSR등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T46" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -4530,6 +4671,9 @@
           <t>SSR등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T47" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -4603,6 +4747,9 @@
           <t>SSR등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T48" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -4676,6 +4823,9 @@
           <t>SSR등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T49" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -4749,6 +4899,9 @@
           <t>SSR등급 레이저</t>
         </is>
       </c>
+      <c r="T50" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -4822,6 +4975,9 @@
           <t>SSR등급 미사일</t>
         </is>
       </c>
+      <c r="T51" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -4895,6 +5051,9 @@
           <t>U등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T52" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -4968,6 +5127,9 @@
           <t>U등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T53" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -5041,6 +5203,9 @@
           <t>U등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T54" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -5114,6 +5279,9 @@
           <t>U등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T55" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -5187,6 +5355,9 @@
           <t>U등급 레이저</t>
         </is>
       </c>
+      <c r="T56" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -5260,6 +5431,9 @@
           <t>U등급 미사일</t>
         </is>
       </c>
+      <c r="T57" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -5333,6 +5507,9 @@
           <t>SU등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T58" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -5406,6 +5583,9 @@
           <t>SU등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T59" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -5479,6 +5659,9 @@
           <t>SU등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T60" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -5552,6 +5735,9 @@
           <t>SU등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T61" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -5625,6 +5811,9 @@
           <t>SU등급 레이저</t>
         </is>
       </c>
+      <c r="T62" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -5698,6 +5887,9 @@
           <t>SU등급 미사일</t>
         </is>
       </c>
+      <c r="T63" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -5771,6 +5963,9 @@
           <t>SSU등급 단발 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T64" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -5844,6 +6039,9 @@
           <t>SSU등급 산탄 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T65" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -5917,6 +6115,9 @@
           <t>SSU등급 속사 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T66" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -5990,6 +6191,9 @@
           <t>SSU등급 관통 (10-24: A줄 x 등급 성장 x 0.5)</t>
         </is>
       </c>
+      <c r="T67" s="7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -6063,6 +6267,9 @@
           <t>SSU등급 레이저</t>
         </is>
       </c>
+      <c r="T68" s="7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -6135,6 +6342,9 @@
         <is>
           <t>SSU등급 미사일</t>
         </is>
+      </c>
+      <c r="T69" s="7" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
